--- a/data/templates/BnF_Opsfit_System.xlsx
+++ b/data/templates/BnF_Opsfit_System.xlsx
@@ -2,96 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="menu" sheetId="1" r:id="R24b5e5140dd849bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipe" sheetId="2" r:id="R31869238c08a46a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ingredients" sheetId="3" r:id="Ra33f7ce130ac4f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="units" sheetId="4" r:id="R9b87315fbc9346cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="menu" sheetId="1" r:id="Rc0bcb04763bc429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipe" sheetId="2" r:id="Rcffd30bf9c704bb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ingredients" sheetId="3" r:id="Redbe2340ed69404a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="units" sheetId="4" r:id="R371b7a0a8ddf449b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="costs" sheetId="5" r:id="R1b7a0392c3c942e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales" sheetId="6" r:id="R9b1c3f65650d41ac"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">Mã món ( food_id ) </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tên món ăn ( food_name )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Size món ( food_size )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Giá bán ( food_price ) </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cơm tấm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">L</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ID công thức ( recipe_id )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ID món ăn ( food_id )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ID nguyên liệu ( ingredient_id )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tên nguyên liệu ( ingredient_name )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lượng dùng ( ingredient_quantity )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">đơn vị dùng ( ingredient_unit )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">thịt heo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">g</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">gạo tấm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">dưa chua</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">dưa leo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cà chua</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tên nguyên liệu (ingredient_name )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Giá hàng ( package_price )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lượng trong gói ( package_quantity )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Đơn vị ( package_unit )</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tỷ lệ hao hụt ( waste_rate )</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
-    <x:numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <x:numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <x:numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <x:numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="200" formatCode="0.######"/>
+  <x:numFmts count="4">
+    <x:numFmt numFmtId="164" formatCode="0.######"/>
+    <x:numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <x:numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <x:numFmt numFmtId="200" formatCode="#,##0"/>
   </x:numFmts>
   <x:fonts count="22">
     <x:font>
@@ -215,7 +146,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="34">
+  <x:fills count="36">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -380,6 +311,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -471,161 +412,174 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="49">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <x:xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <x:xf numFmtId="165" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="44" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="42" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="2" borderId="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="9" xfId="0"/>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="9" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -678,6 +632,74 @@
     <x:cellStyle name="40% - Accent6" xfId="47"/>
     <x:cellStyle name="60% - Accent6" xfId="48"/>
   </x:cellStyles>
+  <x:colors>
+    <x:indexedColors>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008000"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00808000"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="00C0C0C0"/>
+      <x:rgbColor rgb="00808080"/>
+      <x:rgbColor rgb="009999FF"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00FFFFCC"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00660066"/>
+      <x:rgbColor rgb="00FF8080"/>
+      <x:rgbColor rgb="000066CC"/>
+      <x:rgbColor rgb="00CCCCFF"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="0000CCFF"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00CCFFCC"/>
+      <x:rgbColor rgb="00FFFF99"/>
+      <x:rgbColor rgb="0099CCFF"/>
+      <x:rgbColor rgb="00FF99CC"/>
+      <x:rgbColor rgb="00CC99FF"/>
+      <x:rgbColor rgb="00FFCC99"/>
+      <x:rgbColor rgb="003366FF"/>
+      <x:rgbColor rgb="0033CCCC"/>
+      <x:rgbColor rgb="0099CC00"/>
+      <x:rgbColor rgb="00FFCC00"/>
+      <x:rgbColor rgb="00FF9900"/>
+      <x:rgbColor rgb="00FF6600"/>
+      <x:rgbColor rgb="00666699"/>
+      <x:rgbColor rgb="00969696"/>
+      <x:rgbColor rgb="00003366"/>
+      <x:rgbColor rgb="00339966"/>
+      <x:rgbColor rgb="00003300"/>
+      <x:rgbColor rgb="00333300"/>
+      <x:rgbColor rgb="00993300"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00333399"/>
+      <x:rgbColor rgb="00333333"/>
+    </x:indexedColors>
+  </x:colors>
 </x:styleSheet>
 </file>
 
@@ -888,7 +910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <x:cols>
     <x:col min="1" max="1" width="22" customWidth="1"/>
     <x:col min="2" max="3" width="24.42727279663086" customWidth="1"/>
@@ -896,27 +918,39 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>3</x:v>
+      <x:c r="A1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mã món ( food_id ) </x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tên món ăn ( food_name )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Size món ( food_size )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Giá bán ( food_price ) </x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="B2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2">
+      <x:c r="B2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cơm tấm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">L</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" t="n">
         <x:v>30000</x:v>
       </x:c>
     </x:row>
@@ -927,7 +961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <x:cols>
     <x:col min="1" max="1" width="23.42727279663086" customWidth="1"/>
     <x:col min="2" max="2" width="19.85454559326172" customWidth="1"/>
@@ -940,114 +974,170 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H1" t="s">
-        <x:v>11</x:v>
+      <x:c r="A1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ID công thức ( recipe_id )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ID món ăn ( food_id )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tên món ăn ( food_name )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ID nguyên liệu ( ingredient_id )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Size món ( food_size )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tên nguyên liệu ( ingredient_name )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lượng dùng ( ingredient_quantity )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">đơn vị dùng ( ingredient_unit )</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="C2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G2">
+      <x:c r="C2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cơm tấm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">L</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">thịt heo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G2" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H2" t="s">
-        <x:v>13</x:v>
+      <x:c r="H2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="C3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G3">
+      <x:c r="C3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cơm tấm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">L</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">gạo tấm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" t="n">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="H3" t="s">
-        <x:v>13</x:v>
+      <x:c r="H3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="C4" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G4">
+      <x:c r="C4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cơm tấm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">L</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dưa chua</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G4" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H4" t="s">
-        <x:v>13</x:v>
+      <x:c r="H4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="C5" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G5">
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cơm tấm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">L</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dưa leo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H5" t="s">
-        <x:v>13</x:v>
+      <x:c r="H5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="C6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G6">
+      <x:c r="C6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cơm tấm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">L</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cà chua</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H6" t="s">
-        <x:v>13</x:v>
+      <x:c r="H6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1057,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <x:cols>
     <x:col min="1" max="1" width="28.42727279663086" customWidth="1"/>
     <x:col min="2" max="2" width="32.42727279663086" customWidth="1"/>
@@ -1068,107 +1158,139 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>22</x:v>
+      <x:c r="A1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ID nguyên liệu ( ingredient_id )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">tên nguyên liệu (ingredient_name )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Giá hàng ( package_price )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lượng trong gói ( package_quantity )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Đơn vị ( package_unit )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tỷ lệ hao hụt ( waste_rate )</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="B2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C2">
+      <x:c r="B2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">gạo tấm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="D2">
+      <x:c r="D2" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="E2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F2">
+      <x:c r="E2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="B3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3">
+      <x:c r="B3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">thịt heo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="D3">
+      <x:c r="D3" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="E3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F3">
+      <x:c r="E3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="B4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4">
+      <x:c r="B4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dưa chua</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" t="n">
         <x:v>12500</x:v>
       </x:c>
-      <x:c r="D4">
+      <x:c r="D4" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="E4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F4">
+      <x:c r="E4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="B5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C5">
+      <x:c r="B5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dưa leo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="D5">
+      <x:c r="D5" t="n">
         <x:v>800</x:v>
       </x:c>
-      <x:c r="E5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F5">
+      <x:c r="E5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="B6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C6">
+      <x:c r="B6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cà chua</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" t="n">
         <x:v>35000</x:v>
       </x:c>
-      <x:c r="D6">
+      <x:c r="D6" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="E6" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F6">
+      <x:c r="E6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1179,258 +1301,1184 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="19" customWidth="1"/>
+    <x:col min="2" max="2" width="22" customWidth="1"/>
+    <x:col min="3" max="3" width="24" customWidth="1"/>
+    <x:col min="4" max="4" width="23" customWidth="1"/>
+    <x:col min="5" max="5" width="30" customWidth="1"/>
+    <x:col min="6" max="6" width="48" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Mã đơn vị ( unit_code )</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str">
-        <x:v>Tên đơn vị ( unit_name )</x:v>
-      </x:c>
-      <x:c r="C1" s="4" t="str">
-        <x:v>Nhóm đo lường ( unit_group )</x:v>
-      </x:c>
-      <x:c r="D1" s="4" t="str">
-        <x:v>Đơn vị chuẩn ( target_unit )</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="str">
-        <x:v>Hệ số về đơn vị chuẩn ( conversion_factor )</x:v>
-      </x:c>
-      <x:c r="F1" s="4" t="str">
-        <x:v>Tên thay thế, cách nhau bởi | ( aliases )</x:v>
+      <x:c r="A1" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mã đơn vị ( unit_code )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tên đơn vị ( unit_name )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Nhóm đo lường ( unit_group )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Đơn vị chuẩn ( target_unit )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hệ số về đơn vị chuẩn ( conversion_factor )</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tên thay thế, cách nhau bởi | ( aliases )</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>ug</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>microgram</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>mass</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>g</x:v>
-      </x:c>
-      <x:c r="E2" s="5" t="n">
-        <x:v>0.000001</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>mcg|μg|µg</x:v>
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ug</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">microgram</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="6" t="n">
+        <x:v>1e-06</x:v>
+      </x:c>
+      <x:c r="F2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mcg|μg|µg</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>mg</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>milligram</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>mass</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>g</x:v>
-      </x:c>
-      <x:c r="E3" s="5" t="n">
+      <x:c r="A3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mg</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">milligram</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="6" t="n">
         <x:v>0.001</x:v>
       </x:c>
-      <x:c r="F3" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>g</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>gram</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>mass</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>g</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="n">
+      <x:c r="A4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">gram</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F4" t="str">
-        <x:v>gram|grams</x:v>
+      <x:c r="F4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">gram|grams</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>kg</x:v>
-      </x:c>
-      <x:c r="B5" t="str">
-        <x:v>kilogram</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>mass</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>g</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="A5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">kg</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">kilogram</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="6" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="F5" t="str">
-        <x:v>kilogram|kilograms</x:v>
+      <x:c r="F5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">kilogram|kilograms</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>ml</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>millilitre</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>volume</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>ml</x:v>
-      </x:c>
-      <x:c r="E6" s="5" t="n">
+      <x:c r="A6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">millilitre</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">volume</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F6" t="str">
-        <x:v>milliliter|milliliters|millilitre|millilitres</x:v>
+      <x:c r="F6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">milliliter|milliliters|millilitre|millilitres</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>l</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>litre</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>volume</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>ml</x:v>
-      </x:c>
-      <x:c r="E7" s="5" t="n">
+      <x:c r="A7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">l</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">litre</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">volume</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="6" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="F7" t="str">
-        <x:v>liter|liters|litre|litres</x:v>
+      <x:c r="F7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">liter|liters|litre|litres</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>cm^3</x:v>
-      </x:c>
-      <x:c r="B8" t="str">
-        <x:v>cubic centimetre</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>volume</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>ml</x:v>
-      </x:c>
-      <x:c r="E8" s="5" t="n">
+      <x:c r="A8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cm^3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cubic centimetre</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">volume</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F8" t="str">
-        <x:v>cm3|cm³</x:v>
+      <x:c r="F8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cm3|cm³</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>dm^3</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
-        <x:v>cubic decimetre</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>volume</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>ml</x:v>
-      </x:c>
-      <x:c r="E9" s="5" t="n">
+      <x:c r="A9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dm^3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cubic decimetre</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">volume</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="6" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="F9" t="str">
-        <x:v>dm3|dm³</x:v>
+      <x:c r="F9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dm3|dm³</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>m^3</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>cubic metre</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>volume</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>ml</x:v>
-      </x:c>
-      <x:c r="E10" s="5" t="n">
+      <x:c r="A10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">m^3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">cubic metre</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">volume</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="6" t="n">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="F10" t="str">
-        <x:v>m3|m³</x:v>
+      <x:c r="F10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">m3|m³</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>tsp</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>metric teaspoon</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>volume</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>ml</x:v>
-      </x:c>
-      <x:c r="E11" s="5" t="n">
+      <x:c r="A11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">tsp</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">metric teaspoon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">volume</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="6" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F11" t="str">
-        <x:v>teaspoon|teaspoons</x:v>
+      <x:c r="F11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">teaspoon|teaspoons</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>tbsp</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>metric tablespoon</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>volume</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>ml</x:v>
-      </x:c>
-      <x:c r="E12" s="5" t="n">
+      <x:c r="A12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">tbsp</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">metric tablespoon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">volume</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="6" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F12" t="str">
-        <x:v>tablespoon|tablespoons</x:v>
+      <x:c r="F12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">tablespoon|tablespoons</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf601c74a0c234003"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0822972a9e664274"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="42" customHeight="1">
+      <x:c r="A1" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ID chi phí (cost_id)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Nhóm chi phí (cost_category)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tên chi phí (cost_name)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Loại chi phí (cost_type)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Số tiền (amount)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Số tháng phân bổ (period_months)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Thời gian sử dụng hữu ích (useful_life_months)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H1" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Phương thức phân bổ (allocation_method)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">COST_RENT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mặt bằng</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tiền thuê mặt bằng</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FIXED</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="11" t="n">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hợp đồng thuê tháng</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">COST_STAFF</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Nhân sự</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lương nhân viên cố định</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FIXED</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="11" t="n">
+        <x:v>8000000</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lương tháng</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">COST_UTILITIES</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Vận hành</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Điện, nước và Internet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FIXED</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="11" t="n">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ước tính chi phí tháng</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">COST_KITCHEN_EQUIPMENT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Khấu hao</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Khấu hao thiết bị bếp</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FIXED</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="11" t="n">
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="G5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Khấu hao đường thẳng</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="E6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="E7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="E8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="E9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="E10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="E11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="E12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="E13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="E14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="E15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="E16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="E17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="E18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="E19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="E20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="E21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="E22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="E23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="E24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="E25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="E26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="E27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="E28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="E29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="E30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="E31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="E32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="E33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="E34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="E35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="E36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="E37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="E38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="E39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="E40"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="E41"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="E42"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="E43"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="E44"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="E45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="E46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="E47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="E48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="E49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="E50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="E51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="E52"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="E53"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="E54"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="E55"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="E56"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="E57"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="E58"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="E59"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="E60"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="E61"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="E62"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="E63"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="E64"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="E65"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="E66"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="E67"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="E68"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="E69"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="E70"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="E71"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="E72"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="E73"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="E74"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="E75"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="E76"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="E77"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="E78"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="E79"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="E80"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="E81"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="E82"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="E83"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="E84"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="E85"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="E86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="E87"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="E88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="E89"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="E90"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="E91"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="E92"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="E93"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="E94"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="E95"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="E96"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="E97"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="E98"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="E99"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="E100"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="42" customHeight="1">
+      <x:c r="A1" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mã món (item_code)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Số lượng bán tháng (quantity_sold_monthly)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">COM_TAM_L</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="11" t="n">
+        <x:v>1350</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="B3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="B4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="B5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="B6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="B7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="B8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="B9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="B10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="B11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="B12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="B13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="B14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="B15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="B16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="B17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="B18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="B19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="B20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="B21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="B22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="B23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="B24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="B25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="B26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="B27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="B28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="B29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="B30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="B31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="B32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="B33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="B34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="B35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="B36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="B37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="B38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="B39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="B40"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="B41"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="B42"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="B43"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="B44"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="B45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="B46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="B47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="B48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="B49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="B50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="B51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="B52"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="B53"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="B54"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="B55"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="B56"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="B57"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="B58"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="B59"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="B60"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="B61"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="B62"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="B63"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="B64"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="B65"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="B66"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="B67"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="B68"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="B69"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="B70"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="B71"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="B72"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="B73"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="B74"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="B75"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="B76"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="B77"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="B78"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="B79"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="B80"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="B81"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="B82"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="B83"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="B84"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="B85"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="B86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="B87"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="B88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="B89"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="B90"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="B91"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="B92"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="B93"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="B94"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="B95"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="B96"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="B97"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="B98"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="B99"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="B100"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>